--- a/docs/Chiraath-Summary-Oct26.xlsx
+++ b/docs/Chiraath-Summary-Oct26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anooppremachandran/Desktop/CHIRAATH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC9B019-03ED-104B-9FA1-4470C6DE1255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1108B52A-A929-5B4F-B8B2-82C2645CA030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">INVENTORY!$A$1:$T$272</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Purchases!$A$1:$D$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sales!$A$1:$I$334</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="1400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3559" uniqueCount="1402">
   <si>
     <t>Notes:</t>
   </si>
@@ -4142,9 +4142,6 @@
     <t>CHR-76 (XXL Plus white salwar)</t>
   </si>
   <si>
-    <t>CHR-182 (Yellow Linen Saree with Lotus, CHR-217 cream/gold with stars and paisley &amp; cream/gold with flowers, CHR-212 Green elephant print, CHR-245 - Kerala Kasavu Tissue Set Mundu - 2250 advance, 1350 - pending</t>
-  </si>
-  <si>
     <t>Shobhana (Bank cleaning staff)</t>
   </si>
   <si>
@@ -4264,6 +4261,15 @@
   </si>
   <si>
     <t>June 1 - Oct 3</t>
+  </si>
+  <si>
+    <t>Shobhana Husband (Bank cleaning staff)</t>
+  </si>
+  <si>
+    <t>CHR-245 - Kerala Kasavu Tissue Set Mundu - 560 advance, 300 - pending</t>
+  </si>
+  <si>
+    <t>CHR-182 (Yellow Linen Saree with Lotus, CHR-217 cream/gold with stars and paisley &amp; cream/gold with flowers, CHR-212 Green elephant print, CHR-245 - Kerala Kasavu Tissue Set Mundu</t>
   </si>
 </sst>
 </file>
@@ -6106,7 +6112,7 @@
                   <c:v>72915</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>65776</c:v>
+                  <c:v>65746</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>79098</c:v>
@@ -6546,7 +6552,7 @@
                   <c:v>-25168</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-36424</c:v>
+                  <c:v>-36454</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>33250</c:v>
@@ -8220,7 +8226,7 @@
       </c>
       <c r="B4" s="10">
         <f>SUMIFS(Sales!C:C, Sales!I:I, "Completed")</f>
-        <v>570831</v>
+        <v>573541</v>
       </c>
       <c r="E4" s="9" t="str">
         <f>PartnerShares!A3</f>
@@ -8237,7 +8243,7 @@
       </c>
       <c r="B5" s="12">
         <f>SUM(Sales!C:C)</f>
-        <v>582131</v>
+        <v>582101</v>
       </c>
       <c r="E5" s="11" t="str">
         <f>PartnerShares!A4</f>
@@ -8254,7 +8260,7 @@
       </c>
       <c r="B6" s="10">
         <f>B4-B3</f>
-        <v>-26406</v>
+        <v>-23696</v>
       </c>
       <c r="E6" s="9" t="str">
         <f>PartnerShares!A5</f>
@@ -8466,15 +8472,15 @@
       </c>
       <c r="B26" s="10">
         <f>'Cash Pool'!B4</f>
-        <v>498078</v>
+        <v>500788</v>
       </c>
       <c r="C26" s="10">
         <f>'Cash Pool'!D4</f>
-        <v>190315.05539999998</v>
+        <v>191218.56939999998</v>
       </c>
       <c r="D26" s="10">
         <f>'Cash Pool'!E4</f>
-        <v>307762.94460000005</v>
+        <v>309569.43060000002</v>
       </c>
       <c r="E26" s="10">
         <f>'Cash Pool'!F4</f>
@@ -8482,11 +8488,11 @@
       </c>
       <c r="F26" s="13">
         <f>'Cash Pool'!G4</f>
-        <v>170452.91860000003</v>
+        <v>172259.40460000001</v>
       </c>
       <c r="G26" s="17" t="str">
         <f>IF(ROUND(F26,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F26),"#,##0"),IF(ROUND(F26,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F26),"#,##0"),"✓ Settled"))</f>
-        <v>Pay ₹170,453</v>
+        <v>Pay ₹172,259</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1">
@@ -8500,11 +8506,11 @@
       </c>
       <c r="C27" s="12">
         <f>'Cash Pool'!D5</f>
-        <v>190200.88920000001</v>
+        <v>191103.86119999998</v>
       </c>
       <c r="D27" s="12">
         <f>'Cash Pool'!E5</f>
-        <v>-130977.88920000001</v>
+        <v>-131880.86119999998</v>
       </c>
       <c r="E27" s="12">
         <f>'Cash Pool'!F5</f>
@@ -8512,11 +8518,11 @@
       </c>
       <c r="F27" s="14">
         <f>'Cash Pool'!G5</f>
-        <v>-59390.847200000004</v>
+        <v>-60293.819199999984</v>
       </c>
       <c r="G27" s="18" t="str">
         <f>IF(ROUND(F27,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F27),"#,##0"),IF(ROUND(F27,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F27),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹59,391</v>
+        <v>Receive ₹60,294</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1">
@@ -8530,11 +8536,11 @@
       </c>
       <c r="C28" s="10">
         <f>'Cash Pool'!D6</f>
-        <v>190315.05539999998</v>
+        <v>191218.56939999998</v>
       </c>
       <c r="D28" s="10">
         <f>'Cash Pool'!E6</f>
-        <v>-177785.05539999998</v>
+        <v>-178688.56939999998</v>
       </c>
       <c r="E28" s="10">
         <f>'Cash Pool'!F6</f>
@@ -8542,11 +8548,11 @@
       </c>
       <c r="F28" s="13">
         <f>'Cash Pool'!G6</f>
-        <v>-112062.07139999997</v>
+        <v>-112965.58539999997</v>
       </c>
       <c r="G28" s="16" t="str">
         <f>IF(ROUND(F28,0)&gt;0,"Pay ₹"&amp;TEXT(ABS(F28),"#,##0"),IF(ROUND(F28,0)&lt;0,"Receive ₹"&amp;TEXT(ABS(F28),"#,##0"),"✓ Settled"))</f>
-        <v>Receive ₹112,062</v>
+        <v>Receive ₹112,966</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
@@ -8658,7 +8664,7 @@
       </c>
       <c r="B3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46300</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1">
@@ -8674,7 +8680,7 @@
       </c>
       <c r="E5" s="21">
         <f>Summary!B4</f>
-        <v>570831</v>
+        <v>573541</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1">
@@ -8683,7 +8689,7 @@
       </c>
       <c r="B6" s="21">
         <f>Summary!B6</f>
-        <v>-26406</v>
+        <v>-23696</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>71</v>
@@ -8730,7 +8736,7 @@
         <v>47311</v>
       </c>
       <c r="C10" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A10)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A10)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>45448</v>
       </c>
       <c r="D10" s="21">
@@ -8754,7 +8760,7 @@
         <v>5152</v>
       </c>
       <c r="C11" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A11)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>19089</v>
       </c>
       <c r="D11" s="27">
@@ -8778,7 +8784,7 @@
         <v>22172</v>
       </c>
       <c r="C12" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A12)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A12)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>16248</v>
       </c>
       <c r="D12" s="21">
@@ -8795,7 +8801,7 @@
         <v>71002</v>
       </c>
       <c r="C13" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A13)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>54177</v>
       </c>
       <c r="D13" s="27">
@@ -8812,7 +8818,7 @@
         <v>4449</v>
       </c>
       <c r="C14" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A14)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>54393</v>
       </c>
       <c r="D14" s="21">
@@ -8829,7 +8835,7 @@
         <v>98083</v>
       </c>
       <c r="C15" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A15)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>72915</v>
       </c>
       <c r="D15" s="27">
@@ -8846,12 +8852,12 @@
         <v>102200</v>
       </c>
       <c r="C16" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
-        <v>65776</v>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A16)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
+        <v>65746</v>
       </c>
       <c r="D16" s="21">
         <f t="shared" si="0"/>
-        <v>-36424</v>
+        <v>-36454</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1">
@@ -8863,7 +8869,7 @@
         <v>45848</v>
       </c>
       <c r="C17" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A17)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>79098</v>
       </c>
       <c r="D17" s="27">
@@ -8880,7 +8886,7 @@
         <v>-9898</v>
       </c>
       <c r="C18" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A18)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>8960</v>
       </c>
       <c r="D18" s="21">
@@ -8897,7 +8903,7 @@
         <v>5900</v>
       </c>
       <c r="C19" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A19)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A19)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>0</v>
       </c>
       <c r="D19" s="27">
@@ -8914,7 +8920,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="21">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A20)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A20)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>0</v>
       </c>
       <c r="D20" s="21">
@@ -8931,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="27">
-        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$992,"MMM")=$A21)*(YEAR(Sales!$A$2:$A$992)=$B$7)*Sales!$C$2:$C$992),0)</f>
+        <f>IFERROR(SUMPRODUCT((TEXT(Sales!$A$2:$A$993,"MMM")=$A21)*(YEAR(Sales!$A$2:$A$993)=$B$7)*Sales!$C$2:$C$993),0)</f>
         <v>0</v>
       </c>
       <c r="D21" s="27">
@@ -10688,7 +10694,7 @@
         <v>-4202</v>
       </c>
       <c r="D114" s="39" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15" customHeight="1">
@@ -10702,7 +10708,7 @@
         <v>-1620</v>
       </c>
       <c r="D115" s="36" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15" customHeight="1">
@@ -10716,7 +10722,7 @@
         <v>-603</v>
       </c>
       <c r="D116" s="39" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15" customHeight="1">
@@ -10730,7 +10736,7 @@
         <v>-1911</v>
       </c>
       <c r="D117" s="36" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" customHeight="1">
@@ -10744,7 +10750,7 @@
         <v>-1706</v>
       </c>
       <c r="D118" s="39" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" customHeight="1">
@@ -10758,7 +10764,7 @@
         <v>5900</v>
       </c>
       <c r="D119" s="36" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15" customHeight="1">
@@ -12750,7 +12756,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I352"/>
+  <dimension ref="A1:I353"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="10" style="42" customWidth="1"/>
@@ -19261,7 +19267,7 @@
       <c r="F264" s="44"/>
       <c r="G264" s="44"/>
       <c r="H264" s="44" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="I264" s="44" t="s">
         <v>355</v>
@@ -19357,7 +19363,7 @@
       <c r="F268" s="44"/>
       <c r="G268" s="44"/>
       <c r="H268" s="44" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="I268" s="44" t="s">
         <v>355</v>
@@ -19943,377 +19949,377 @@
         <v>46229</v>
       </c>
       <c r="B292" s="45" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C292" s="85">
-        <v>3600</v>
-      </c>
-      <c r="D292" s="45"/>
-      <c r="E292" s="45"/>
+        <v>2710</v>
+      </c>
+      <c r="D292" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E292" s="45" t="s">
+        <v>49</v>
+      </c>
       <c r="F292" s="46"/>
       <c r="G292" s="46"/>
       <c r="H292" s="46" t="s">
-        <v>1359</v>
+        <v>1401</v>
       </c>
       <c r="I292" s="45" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" ht="14">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" ht="28">
       <c r="A293" s="84">
         <v>46229</v>
       </c>
       <c r="B293" s="45" t="s">
-        <v>1087</v>
+        <v>1399</v>
       </c>
       <c r="C293" s="85">
-        <v>2230</v>
-      </c>
-      <c r="D293" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="E293" s="45" t="s">
-        <v>49</v>
-      </c>
+        <v>860</v>
+      </c>
+      <c r="D293" s="45"/>
+      <c r="E293" s="45"/>
       <c r="F293" s="46"/>
       <c r="G293" s="46"/>
       <c r="H293" s="46" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I293" s="45" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" ht="14">
+      <c r="A294" s="84">
+        <v>46229</v>
+      </c>
+      <c r="B294" s="45" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C294" s="85">
+        <v>2230</v>
+      </c>
+      <c r="D294" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E294" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F294" s="46"/>
+      <c r="G294" s="46"/>
+      <c r="H294" s="46" t="s">
         <v>1277</v>
       </c>
-      <c r="I293" s="45" t="s">
+      <c r="I294" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="28">
-      <c r="A294" s="82">
+    <row r="295" spans="1:9" ht="28">
+      <c r="A295" s="82">
         <v>46229</v>
       </c>
-      <c r="B294" s="44" t="s">
+      <c r="B295" s="44" t="s">
         <v>1162</v>
       </c>
-      <c r="C294" s="83">
+      <c r="C295" s="83">
         <v>3700</v>
       </c>
-      <c r="D294" s="44" t="s">
+      <c r="D295" s="44" t="s">
         <v>1267</v>
       </c>
-      <c r="E294" s="44" t="s">
+      <c r="E295" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F294" s="44"/>
-      <c r="G294" s="44"/>
-      <c r="H294" s="44" t="s">
+      <c r="F295" s="44"/>
+      <c r="G295" s="44"/>
+      <c r="H295" s="44" t="s">
         <v>1268</v>
       </c>
-      <c r="I294" s="44" t="s">
+      <c r="I295" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="14">
-      <c r="A295" s="84">
+    <row r="296" spans="1:9" ht="14">
+      <c r="A296" s="84">
         <v>46235</v>
       </c>
-      <c r="B295" s="45" t="s">
+      <c r="B296" s="45" t="s">
         <v>1200</v>
       </c>
-      <c r="C295" s="85">
+      <c r="C296" s="85">
         <v>1450</v>
       </c>
-      <c r="D295" s="45" t="s">
+      <c r="D296" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E295" s="45" t="s">
+      <c r="E296" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F295" s="46"/>
-      <c r="G295" s="46"/>
-      <c r="H295" s="46" t="s">
+      <c r="F296" s="46"/>
+      <c r="G296" s="46"/>
+      <c r="H296" s="46" t="s">
         <v>1199</v>
       </c>
-      <c r="I295" s="45" t="s">
+      <c r="I296" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="14">
-      <c r="A296" s="82">
+    <row r="297" spans="1:9" ht="14">
+      <c r="A297" s="82">
         <v>46236</v>
       </c>
-      <c r="B296" s="44" t="s">
+      <c r="B297" s="44" t="s">
         <v>1271</v>
       </c>
-      <c r="C296" s="83">
+      <c r="C297" s="83">
         <v>6900</v>
       </c>
-      <c r="D296" s="44" t="s">
+      <c r="D297" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E296" s="44" t="s">
+      <c r="E297" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F296" s="44"/>
-      <c r="G296" s="44"/>
-      <c r="H296" s="44" t="s">
+      <c r="F297" s="44"/>
+      <c r="G297" s="44"/>
+      <c r="H297" s="44" t="s">
         <v>1273</v>
       </c>
-      <c r="I296" s="44" t="s">
+      <c r="I297" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="14">
-      <c r="A297" s="84">
+    <row r="298" spans="1:9" ht="14">
+      <c r="A298" s="84">
         <v>46236</v>
       </c>
-      <c r="B297" s="45" t="s">
+      <c r="B298" s="45" t="s">
         <v>1203</v>
       </c>
-      <c r="C297" s="85">
+      <c r="C298" s="85">
         <v>1479</v>
       </c>
-      <c r="D297" s="45" t="s">
+      <c r="D298" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E297" s="45" t="s">
+      <c r="E298" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F297" s="46"/>
-      <c r="G297" s="46"/>
-      <c r="H297" s="46" t="s">
+      <c r="F298" s="46"/>
+      <c r="G298" s="46"/>
+      <c r="H298" s="46" t="s">
         <v>1202</v>
       </c>
-      <c r="I297" s="45" t="s">
+      <c r="I298" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="14">
-      <c r="A298" s="82">
+    <row r="299" spans="1:9" ht="14">
+      <c r="A299" s="82">
         <v>46236</v>
       </c>
-      <c r="B298" s="44" t="s">
+      <c r="B299" s="44" t="s">
         <v>1207</v>
       </c>
-      <c r="C298" s="83">
+      <c r="C299" s="83">
         <v>2630</v>
       </c>
-      <c r="D298" s="44" t="s">
+      <c r="D299" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E298" s="44" t="s">
+      <c r="E299" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F298" s="44"/>
-      <c r="G298" s="44"/>
-      <c r="H298" s="44" t="s">
+      <c r="F299" s="44"/>
+      <c r="G299" s="44"/>
+      <c r="H299" s="44" t="s">
         <v>1205</v>
       </c>
-      <c r="I298" s="44" t="s">
+      <c r="I299" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="14">
-      <c r="A299" s="84">
+    <row r="300" spans="1:9" ht="14">
+      <c r="A300" s="84">
         <v>46238</v>
       </c>
-      <c r="B299" s="45" t="s">
+      <c r="B300" s="45" t="s">
         <v>1084</v>
       </c>
-      <c r="C299" s="85">
+      <c r="C300" s="85">
         <v>1380</v>
       </c>
-      <c r="D299" s="45" t="s">
+      <c r="D300" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E299" s="45" t="s">
+      <c r="E300" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F299" s="46"/>
-      <c r="G299" s="46"/>
-      <c r="H299" s="46" t="s">
+      <c r="F300" s="46"/>
+      <c r="G300" s="46"/>
+      <c r="H300" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="I299" s="45" t="s">
+      <c r="I300" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="14">
-      <c r="A300" s="82">
+    <row r="301" spans="1:9" ht="14">
+      <c r="A301" s="82">
         <v>46238</v>
       </c>
-      <c r="B300" s="44" t="s">
+      <c r="B301" s="44" t="s">
         <v>1271</v>
       </c>
-      <c r="C300" s="83">
+      <c r="C301" s="83">
         <v>12650</v>
       </c>
-      <c r="D300" s="44" t="s">
+      <c r="D301" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E300" s="44" t="s">
+      <c r="E301" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F300" s="44"/>
-      <c r="G300" s="44"/>
-      <c r="H300" s="44" t="s">
+      <c r="F301" s="44"/>
+      <c r="G301" s="44"/>
+      <c r="H301" s="44" t="s">
         <v>1274</v>
       </c>
-      <c r="I300" s="44" t="s">
+      <c r="I301" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="14">
-      <c r="A301" s="84">
+    <row r="302" spans="1:9" ht="14">
+      <c r="A302" s="84">
         <v>46240</v>
       </c>
-      <c r="B301" s="45" t="s">
+      <c r="B302" s="45" t="s">
         <v>1203</v>
       </c>
-      <c r="C301" s="85">
+      <c r="C302" s="85">
         <v>1000</v>
       </c>
-      <c r="D301" s="45"/>
-      <c r="E301" s="45"/>
-      <c r="F301" s="46"/>
-      <c r="G301" s="46"/>
-      <c r="H301" s="46" t="s">
+      <c r="D302" s="45"/>
+      <c r="E302" s="45"/>
+      <c r="F302" s="46"/>
+      <c r="G302" s="46"/>
+      <c r="H302" s="46" t="s">
         <v>1212</v>
       </c>
-      <c r="I301" s="45" t="s">
+      <c r="I302" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="28">
-      <c r="A302" s="82">
+    <row r="303" spans="1:9" ht="28">
+      <c r="A303" s="82">
         <v>46241</v>
       </c>
-      <c r="B302" s="44" t="s">
+      <c r="B303" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="C302" s="83">
+      <c r="C303" s="83">
         <v>4750</v>
       </c>
-      <c r="D302" s="44" t="s">
+      <c r="D303" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E302" s="44" t="s">
+      <c r="E303" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F302" s="44"/>
-      <c r="G302" s="44"/>
-      <c r="H302" s="44" t="s">
-        <v>1363</v>
-      </c>
-      <c r="I302" s="44" t="s">
+      <c r="F303" s="44"/>
+      <c r="G303" s="44"/>
+      <c r="H303" s="44" t="s">
+        <v>1362</v>
+      </c>
+      <c r="I303" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="14">
-      <c r="A303" s="84">
+    <row r="304" spans="1:9" ht="14">
+      <c r="A304" s="84">
         <v>46243</v>
       </c>
-      <c r="B303" s="45" t="s">
+      <c r="B304" s="45" t="s">
         <v>1246</v>
       </c>
-      <c r="C303" s="85">
+      <c r="C304" s="85">
         <v>950</v>
       </c>
-      <c r="D303" s="45" t="s">
+      <c r="D304" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E303" s="45" t="s">
+      <c r="E304" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F303" s="46"/>
-      <c r="G303" s="46"/>
-      <c r="H303" s="46" t="s">
+      <c r="F304" s="46"/>
+      <c r="G304" s="46"/>
+      <c r="H304" s="46" t="s">
         <v>1357</v>
       </c>
-      <c r="I303" s="45" t="s">
+      <c r="I304" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="14">
-      <c r="A304" s="82">
+    <row r="305" spans="1:9" ht="14">
+      <c r="A305" s="82">
         <v>46243</v>
       </c>
-      <c r="B304" s="44" t="s">
+      <c r="B305" s="44" t="s">
         <v>1247</v>
       </c>
-      <c r="C304" s="83">
+      <c r="C305" s="83">
         <v>1380</v>
       </c>
-      <c r="D304" s="44" t="s">
+      <c r="D305" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E304" s="44" t="s">
+      <c r="E305" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F304" s="44"/>
-      <c r="G304" s="44"/>
-      <c r="H304" s="44" t="s">
+      <c r="F305" s="44"/>
+      <c r="G305" s="44"/>
+      <c r="H305" s="44" t="s">
         <v>1248</v>
       </c>
-      <c r="I304" s="44" t="s">
+      <c r="I305" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="14">
-      <c r="A305" s="84">
+    <row r="306" spans="1:9" ht="14">
+      <c r="A306" s="84">
         <v>46243</v>
       </c>
-      <c r="B305" s="45" t="s">
+      <c r="B306" s="45" t="s">
         <v>1249</v>
       </c>
-      <c r="C305" s="85">
+      <c r="C306" s="85">
         <v>1250</v>
       </c>
-      <c r="D305" s="45" t="s">
+      <c r="D306" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E305" s="45" t="s">
+      <c r="E306" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F305" s="46"/>
-      <c r="G305" s="46"/>
-      <c r="H305" s="46" t="s">
+      <c r="F306" s="46"/>
+      <c r="G306" s="46"/>
+      <c r="H306" s="46" t="s">
         <v>1250</v>
       </c>
-      <c r="I305" s="45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" ht="14">
-      <c r="A306" s="82">
-        <v>46243</v>
-      </c>
-      <c r="B306" s="44" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C306" s="83">
-        <v>5750</v>
-      </c>
-      <c r="D306" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="E306" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="F306" s="44"/>
-      <c r="G306" s="44"/>
-      <c r="H306" s="44" t="s">
-        <v>1272</v>
-      </c>
-      <c r="I306" s="44" t="s">
+      <c r="I306" s="45" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="307" spans="1:9" ht="14">
       <c r="A307" s="82">
-        <v>46248</v>
+        <v>46243</v>
       </c>
       <c r="B307" s="44" t="s">
-        <v>1252</v>
+        <v>1271</v>
       </c>
       <c r="C307" s="83">
-        <v>1380</v>
+        <v>5750</v>
       </c>
       <c r="D307" s="44" t="s">
         <v>161</v>
@@ -20324,875 +20330,900 @@
       <c r="F307" s="44"/>
       <c r="G307" s="44"/>
       <c r="H307" s="44" t="s">
-        <v>1253</v>
+        <v>1272</v>
       </c>
       <c r="I307" s="44" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="308" spans="1:9" ht="14">
-      <c r="A308" s="84">
+      <c r="A308" s="82">
         <v>46248</v>
       </c>
-      <c r="B308" s="45" t="s">
+      <c r="B308" s="44" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C308" s="83">
+        <v>1380</v>
+      </c>
+      <c r="D308" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="E308" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F308" s="44"/>
+      <c r="G308" s="44"/>
+      <c r="H308" s="44" t="s">
+        <v>1253</v>
+      </c>
+      <c r="I308" s="44" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" ht="14">
+      <c r="A309" s="84">
+        <v>46248</v>
+      </c>
+      <c r="B309" s="45" t="s">
         <v>1254</v>
       </c>
-      <c r="C308" s="85">
+      <c r="C309" s="85">
         <v>1380</v>
       </c>
-      <c r="D308" s="45" t="s">
+      <c r="D309" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E308" s="45" t="s">
+      <c r="E309" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F308" s="46"/>
-      <c r="G308" s="46"/>
-      <c r="H308" s="46" t="s">
+      <c r="F309" s="46"/>
+      <c r="G309" s="46"/>
+      <c r="H309" s="46" t="s">
         <v>1255</v>
       </c>
-      <c r="I308" s="45" t="s">
+      <c r="I309" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="14">
-      <c r="A309" s="82">
+    <row r="310" spans="1:9" ht="14">
+      <c r="A310" s="82">
         <v>46250</v>
       </c>
-      <c r="B309" s="44" t="s">
+      <c r="B310" s="44" t="s">
         <v>328</v>
       </c>
-      <c r="C309" s="83">
+      <c r="C310" s="83">
         <v>1979</v>
       </c>
-      <c r="D309" s="44" t="s">
+      <c r="D310" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E309" s="44" t="s">
+      <c r="E310" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F309" s="44"/>
-      <c r="G309" s="44"/>
-      <c r="H309" s="44" t="s">
+      <c r="F310" s="44"/>
+      <c r="G310" s="44"/>
+      <c r="H310" s="44" t="s">
         <v>1264</v>
       </c>
-      <c r="I309" s="44" t="s">
+      <c r="I310" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="14">
-      <c r="A310" s="84">
+    <row r="311" spans="1:9" ht="14">
+      <c r="A311" s="84">
         <v>46250</v>
       </c>
-      <c r="B310" s="45" t="s">
+      <c r="B311" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="C310" s="85">
+      <c r="C311" s="85">
         <v>980</v>
       </c>
-      <c r="D310" s="45" t="s">
+      <c r="D311" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E310" s="45" t="s">
+      <c r="E311" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F310" s="46"/>
-      <c r="G310" s="46"/>
-      <c r="H310" s="46" t="s">
+      <c r="F311" s="46"/>
+      <c r="G311" s="46"/>
+      <c r="H311" s="46" t="s">
         <v>1257</v>
       </c>
-      <c r="I310" s="45" t="s">
+      <c r="I311" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="14">
-      <c r="A311" s="82">
+    <row r="312" spans="1:9" ht="14">
+      <c r="A312" s="82">
         <v>46250</v>
       </c>
-      <c r="B311" s="44" t="s">
+      <c r="B312" s="44" t="s">
         <v>1260</v>
       </c>
-      <c r="C311" s="83">
+      <c r="C312" s="83">
         <v>2250</v>
       </c>
-      <c r="D311" s="44" t="s">
+      <c r="D312" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E311" s="44" t="s">
+      <c r="E312" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F311" s="44"/>
-      <c r="G311" s="44"/>
-      <c r="H311" s="44" t="s">
+      <c r="F312" s="44"/>
+      <c r="G312" s="44"/>
+      <c r="H312" s="44" t="s">
         <v>1262</v>
       </c>
-      <c r="I311" s="44" t="s">
+      <c r="I312" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="14">
-      <c r="A312" s="84">
+    <row r="313" spans="1:9" ht="14">
+      <c r="A313" s="84">
         <v>46252</v>
       </c>
-      <c r="B312" s="45" t="s">
+      <c r="B313" s="45" t="s">
         <v>1271</v>
       </c>
-      <c r="C312" s="85">
+      <c r="C313" s="85">
         <v>5750</v>
       </c>
-      <c r="D312" s="45" t="s">
+      <c r="D313" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E312" s="45" t="s">
+      <c r="E313" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F312" s="46"/>
-      <c r="G312" s="46"/>
-      <c r="H312" s="46" t="s">
+      <c r="F313" s="46"/>
+      <c r="G313" s="46"/>
+      <c r="H313" s="46" t="s">
         <v>1272</v>
       </c>
-      <c r="I312" s="45" t="s">
+      <c r="I313" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="14">
-      <c r="A313" s="82">
+    <row r="314" spans="1:9" ht="14">
+      <c r="A314" s="82">
         <v>46252</v>
       </c>
-      <c r="B313" s="44" t="s">
+      <c r="B314" s="44" t="s">
         <v>1275</v>
       </c>
-      <c r="C313" s="83">
+      <c r="C314" s="83">
         <v>1380</v>
       </c>
-      <c r="D313" s="44" t="s">
+      <c r="D314" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E313" s="44" t="s">
+      <c r="E314" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F313" s="44"/>
-      <c r="G313" s="44"/>
-      <c r="H313" s="44" t="s">
+      <c r="F314" s="44"/>
+      <c r="G314" s="44"/>
+      <c r="H314" s="44" t="s">
         <v>1286</v>
       </c>
-      <c r="I313" s="44" t="s">
+      <c r="I314" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="14">
-      <c r="A314" s="84">
+    <row r="315" spans="1:9" ht="14">
+      <c r="A315" s="84">
         <v>46252</v>
       </c>
-      <c r="B314" s="45" t="s">
+      <c r="B315" s="45" t="s">
         <v>1271</v>
       </c>
-      <c r="C314" s="85">
+      <c r="C315" s="85">
         <v>5750</v>
       </c>
-      <c r="D314" s="45" t="s">
+      <c r="D315" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E314" s="45" t="s">
+      <c r="E315" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F314" s="46"/>
-      <c r="G314" s="46"/>
-      <c r="H314" s="46" t="s">
+      <c r="F315" s="46"/>
+      <c r="G315" s="46"/>
+      <c r="H315" s="46" t="s">
         <v>1272</v>
       </c>
-      <c r="I314" s="45" t="s">
+      <c r="I315" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="14">
-      <c r="A315" s="82">
+    <row r="316" spans="1:9" ht="14">
+      <c r="A316" s="82">
         <v>46252</v>
       </c>
-      <c r="B315" s="44" t="s">
+      <c r="B316" s="44" t="s">
         <v>1279</v>
       </c>
-      <c r="C315" s="83">
+      <c r="C316" s="83">
         <v>1340</v>
       </c>
-      <c r="D315" s="44" t="s">
+      <c r="D316" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E315" s="44" t="s">
+      <c r="E316" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F315" s="44"/>
-      <c r="G315" s="44"/>
-      <c r="H315" s="44" t="s">
+      <c r="F316" s="44"/>
+      <c r="G316" s="44"/>
+      <c r="H316" s="44" t="s">
         <v>1280</v>
       </c>
-      <c r="I315" s="44" t="s">
+      <c r="I316" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="14">
-      <c r="A316" s="84">
+    <row r="317" spans="1:9" ht="14">
+      <c r="A317" s="84">
         <v>46252</v>
       </c>
-      <c r="B316" s="45" t="s">
+      <c r="B317" s="45" t="s">
         <v>1282</v>
       </c>
-      <c r="C316" s="85">
+      <c r="C317" s="85">
         <v>1250</v>
       </c>
-      <c r="D316" s="45" t="s">
+      <c r="D317" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E316" s="45" t="s">
+      <c r="E317" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F316" s="46"/>
-      <c r="G316" s="46"/>
-      <c r="H316" s="46" t="s">
+      <c r="F317" s="46"/>
+      <c r="G317" s="46"/>
+      <c r="H317" s="46" t="s">
         <v>1283</v>
       </c>
-      <c r="I316" s="45" t="s">
+      <c r="I317" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="14">
-      <c r="A317" s="82">
+    <row r="318" spans="1:9" ht="14">
+      <c r="A318" s="82">
         <v>46257</v>
       </c>
-      <c r="B317" s="44" t="s">
+      <c r="B318" s="44" t="s">
         <v>1271</v>
       </c>
-      <c r="C317" s="83">
+      <c r="C318" s="83">
         <v>1780</v>
       </c>
-      <c r="D317" s="44" t="s">
+      <c r="D318" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E317" s="44" t="s">
+      <c r="E318" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F317" s="44"/>
-      <c r="G317" s="44"/>
-      <c r="H317" s="44" t="s">
+      <c r="F318" s="44"/>
+      <c r="G318" s="44"/>
+      <c r="H318" s="44" t="s">
         <v>1287</v>
       </c>
-      <c r="I317" s="44" t="s">
+      <c r="I318" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="14">
-      <c r="A318" s="84">
+    <row r="319" spans="1:9" ht="14">
+      <c r="A319" s="84">
         <v>46257</v>
       </c>
-      <c r="B318" s="45" t="s">
+      <c r="B319" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="C318" s="85">
+      <c r="C319" s="85">
         <v>2100</v>
       </c>
-      <c r="D318" s="45" t="s">
+      <c r="D319" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E318" s="45" t="s">
+      <c r="E319" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F318" s="46"/>
-      <c r="G318" s="46"/>
-      <c r="H318" s="46" t="s">
+      <c r="F319" s="46"/>
+      <c r="G319" s="46"/>
+      <c r="H319" s="46" t="s">
         <v>1290</v>
       </c>
-      <c r="I318" s="45" t="s">
+      <c r="I319" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="14">
-      <c r="A319" s="82">
+    <row r="320" spans="1:9" ht="14">
+      <c r="A320" s="82">
         <v>46257</v>
       </c>
-      <c r="B319" s="44" t="s">
+      <c r="B320" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C319" s="83">
+      <c r="C320" s="83">
         <v>700</v>
       </c>
-      <c r="D319" s="44" t="s">
+      <c r="D320" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E319" s="44" t="s">
+      <c r="E320" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F319" s="44"/>
-      <c r="G319" s="44"/>
-      <c r="H319" s="44" t="s">
+      <c r="F320" s="44"/>
+      <c r="G320" s="44"/>
+      <c r="H320" s="44" t="s">
         <v>1291</v>
       </c>
-      <c r="I319" s="44" t="s">
+      <c r="I320" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="14">
-      <c r="A320" s="84">
+    <row r="321" spans="1:9" ht="14">
+      <c r="A321" s="84">
         <v>46257</v>
       </c>
-      <c r="B320" s="45" t="s">
+      <c r="B321" s="45" t="s">
         <v>1294</v>
       </c>
-      <c r="C320" s="85">
+      <c r="C321" s="85">
         <v>1500</v>
       </c>
-      <c r="D320" s="45" t="s">
+      <c r="D321" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E320" s="45" t="s">
+      <c r="E321" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F320" s="46"/>
-      <c r="G320" s="46"/>
-      <c r="H320" s="46" t="s">
+      <c r="F321" s="46"/>
+      <c r="G321" s="46"/>
+      <c r="H321" s="46" t="s">
         <v>1295</v>
       </c>
-      <c r="I320" s="45" t="s">
+      <c r="I321" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="14">
-      <c r="A321" s="82">
+    <row r="322" spans="1:9" ht="14">
+      <c r="A322" s="82">
         <v>46258</v>
       </c>
-      <c r="B321" s="44" t="s">
+      <c r="B322" s="44" t="s">
         <v>1296</v>
       </c>
-      <c r="C321" s="83">
+      <c r="C322" s="83">
         <v>1250</v>
       </c>
-      <c r="D321" s="44" t="s">
+      <c r="D322" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E321" s="44" t="s">
+      <c r="E322" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F321" s="44"/>
-      <c r="G321" s="44"/>
-      <c r="H321" s="44" t="s">
+      <c r="F322" s="44"/>
+      <c r="G322" s="44"/>
+      <c r="H322" s="44" t="s">
         <v>1297</v>
       </c>
-      <c r="I321" s="44" t="s">
+      <c r="I322" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="14">
-      <c r="A322" s="84">
+    <row r="323" spans="1:9" ht="14">
+      <c r="A323" s="84">
         <v>46263</v>
       </c>
-      <c r="B322" s="45" t="s">
+      <c r="B323" s="45" t="s">
         <v>1312</v>
       </c>
-      <c r="C322" s="85">
+      <c r="C323" s="85">
         <v>1380</v>
       </c>
-      <c r="D322" s="45" t="s">
+      <c r="D323" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E322" s="45" t="s">
+      <c r="E323" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F322" s="46"/>
-      <c r="G322" s="46"/>
-      <c r="H322" s="46" t="s">
+      <c r="F323" s="46"/>
+      <c r="G323" s="46"/>
+      <c r="H323" s="46" t="s">
         <v>1313</v>
       </c>
-      <c r="I322" s="45" t="s">
+      <c r="I323" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="14">
-      <c r="A323" s="82">
+    <row r="324" spans="1:9" ht="14">
+      <c r="A324" s="82">
         <v>46263</v>
       </c>
-      <c r="B323" s="44" t="s">
+      <c r="B324" s="44" t="s">
         <v>1315</v>
       </c>
-      <c r="C323" s="83">
+      <c r="C324" s="83">
         <v>1380</v>
       </c>
-      <c r="D323" s="44" t="s">
+      <c r="D324" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E323" s="44" t="s">
+      <c r="E324" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F323" s="44"/>
-      <c r="G323" s="44"/>
-      <c r="H323" s="44" t="s">
+      <c r="F324" s="44"/>
+      <c r="G324" s="44"/>
+      <c r="H324" s="44" t="s">
         <v>1316</v>
       </c>
-      <c r="I323" s="44" t="s">
+      <c r="I324" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="14">
-      <c r="A324" s="84">
+    <row r="325" spans="1:9" ht="14">
+      <c r="A325" s="84">
         <v>46263</v>
       </c>
-      <c r="B324" s="45" t="s">
+      <c r="B325" s="45" t="s">
         <v>1317</v>
       </c>
-      <c r="C324" s="85">
+      <c r="C325" s="85">
         <v>2500</v>
       </c>
-      <c r="D324" s="45" t="s">
+      <c r="D325" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E324" s="45" t="s">
+      <c r="E325" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="F324" s="46"/>
-      <c r="G324" s="46"/>
-      <c r="H324" s="46" t="s">
+      <c r="F325" s="46"/>
+      <c r="G325" s="46"/>
+      <c r="H325" s="46" t="s">
         <v>1327</v>
       </c>
-      <c r="I324" s="45" t="s">
+      <c r="I325" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="14">
-      <c r="A325" s="82">
+    <row r="326" spans="1:9" ht="14">
+      <c r="A326" s="82">
         <v>46257</v>
       </c>
-      <c r="B325" s="44" t="s">
+      <c r="B326" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="C325" s="83">
+      <c r="C326" s="83">
         <v>750</v>
       </c>
-      <c r="D325" s="44" t="s">
+      <c r="D326" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="E325" s="44" t="s">
+      <c r="E326" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F325" s="44"/>
-      <c r="G325" s="44"/>
-      <c r="H325" s="44" t="s">
+      <c r="F326" s="44"/>
+      <c r="G326" s="44"/>
+      <c r="H326" s="44" t="s">
         <v>1326</v>
       </c>
-      <c r="I325" s="44" t="s">
+      <c r="I326" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="14">
-      <c r="A326" s="84">
+    <row r="327" spans="1:9" ht="14">
+      <c r="A327" s="84">
         <v>46257</v>
       </c>
-      <c r="B326" s="45" t="s">
+      <c r="B327" s="45" t="s">
         <v>1328</v>
       </c>
-      <c r="C326" s="85">
+      <c r="C327" s="85">
         <v>750</v>
       </c>
-      <c r="D326" s="45" t="s">
+      <c r="D327" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="E326" s="45" t="s">
+      <c r="E327" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="F326" s="46"/>
-      <c r="G326" s="46"/>
-      <c r="H326" s="46" t="s">
+      <c r="F327" s="46"/>
+      <c r="G327" s="46"/>
+      <c r="H327" s="46" t="s">
         <v>1329</v>
       </c>
-      <c r="I326" s="45" t="s">
+      <c r="I327" s="45" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="14">
-      <c r="A327" s="82">
+    <row r="328" spans="1:9" ht="14">
+      <c r="A328" s="82">
         <v>46275</v>
       </c>
-      <c r="B327" s="44" t="s">
+      <c r="B328" s="44" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C328" s="83">
+        <v>1380</v>
+      </c>
+      <c r="D328" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="E328" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F328" s="44"/>
+      <c r="G328" s="44"/>
+      <c r="H328" s="44" t="s">
         <v>1364</v>
       </c>
-      <c r="C327" s="83">
+      <c r="I328" s="44" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" ht="14">
+      <c r="A329" s="84">
+        <v>46272</v>
+      </c>
+      <c r="B329" s="45" t="s">
+        <v>413</v>
+      </c>
+      <c r="C329" s="85">
+        <v>2400</v>
+      </c>
+      <c r="D329" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E329" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="F329" s="46"/>
+      <c r="G329" s="46"/>
+      <c r="H329" s="46" t="s">
+        <v>1365</v>
+      </c>
+      <c r="I329" s="45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" ht="14">
+      <c r="A330" s="82">
+        <v>46275</v>
+      </c>
+      <c r="B330" s="44" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C330" s="83">
+        <v>1450</v>
+      </c>
+      <c r="D330" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E330" s="44" t="s">
+        <v>50</v>
+      </c>
+      <c r="F330" s="44"/>
+      <c r="G330" s="44"/>
+      <c r="H330" s="44" t="s">
+        <v>1370</v>
+      </c>
+      <c r="I330" s="44" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" ht="14">
+      <c r="A331" s="84">
+        <v>46275</v>
+      </c>
+      <c r="B331" s="45" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C331" s="85">
+        <v>950</v>
+      </c>
+      <c r="D331" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="E331" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="F331" s="46"/>
+      <c r="G331" s="46"/>
+      <c r="H331" s="46" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I331" s="45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" ht="14">
+      <c r="A332" s="82">
+        <v>46277</v>
+      </c>
+      <c r="B332" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="C332" s="83">
+        <v>650</v>
+      </c>
+      <c r="D332" s="44" t="s">
+        <v>149</v>
+      </c>
+      <c r="E332" s="44" t="s">
+        <v>49</v>
+      </c>
+      <c r="F332" s="44"/>
+      <c r="G332" s="44"/>
+      <c r="H332" s="44" t="s">
+        <v>1383</v>
+      </c>
+      <c r="I332" s="44" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" ht="14">
+      <c r="A333" s="84">
+        <v>46277</v>
+      </c>
+      <c r="B333" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C333" s="85">
+        <v>750</v>
+      </c>
+      <c r="D333" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="E333" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="F333" s="46"/>
+      <c r="G333" s="46"/>
+      <c r="H333" s="46" t="s">
+        <v>1384</v>
+      </c>
+      <c r="I333" s="45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" ht="14">
+      <c r="A334" s="82">
+        <v>46277</v>
+      </c>
+      <c r="B334" s="44" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C334" s="83">
         <v>1380</v>
       </c>
-      <c r="D327" s="44" t="s">
+      <c r="D334" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E327" s="44" t="s">
+      <c r="E334" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="F327" s="44"/>
-      <c r="G327" s="44"/>
-      <c r="H327" s="44" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I327" s="44" t="s">
+      <c r="F334" s="44"/>
+      <c r="G334" s="44"/>
+      <c r="H334" s="44" t="s">
+        <v>1364</v>
+      </c>
+      <c r="I334" s="44" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="14">
-      <c r="A328" s="84">
-        <v>46272</v>
-      </c>
-      <c r="B328" s="45" t="s">
-        <v>413</v>
-      </c>
-      <c r="C328" s="85">
-        <v>2400</v>
-      </c>
-      <c r="D328" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="E328" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="F328" s="46"/>
-      <c r="G328" s="46"/>
-      <c r="H328" s="46" t="s">
-        <v>1366</v>
-      </c>
-      <c r="I328" s="45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" ht="14">
-      <c r="A329" s="82">
-        <v>46275</v>
-      </c>
-      <c r="B329" s="44" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C329" s="83">
-        <v>1450</v>
-      </c>
-      <c r="D329" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="E329" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="F329" s="44"/>
-      <c r="G329" s="44"/>
-      <c r="H329" s="44" t="s">
-        <v>1371</v>
-      </c>
-      <c r="I329" s="44" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="330" spans="1:9" ht="14">
-      <c r="A330" s="84">
-        <v>46275</v>
-      </c>
-      <c r="B330" s="45" t="s">
-        <v>1375</v>
-      </c>
-      <c r="C330" s="85">
-        <v>950</v>
-      </c>
-      <c r="D330" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="E330" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="F330" s="46"/>
-      <c r="G330" s="46"/>
-      <c r="H330" s="46" t="s">
-        <v>1376</v>
-      </c>
-      <c r="I330" s="45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="331" spans="1:9" ht="14">
-      <c r="A331" s="82">
-        <v>46277</v>
-      </c>
-      <c r="B331" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="C331" s="83">
-        <v>650</v>
-      </c>
-      <c r="D331" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="E331" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="F331" s="44"/>
-      <c r="G331" s="44"/>
-      <c r="H331" s="44" t="s">
-        <v>1384</v>
-      </c>
-      <c r="I331" s="44" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="332" spans="1:9" ht="14">
-      <c r="A332" s="84">
-        <v>46277</v>
-      </c>
-      <c r="B332" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="C332" s="85">
-        <v>750</v>
-      </c>
-      <c r="D332" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="E332" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="F332" s="46"/>
-      <c r="G332" s="46"/>
-      <c r="H332" s="46" t="s">
-        <v>1385</v>
-      </c>
-      <c r="I332" s="45" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="333" spans="1:9" ht="14">
-      <c r="A333" s="82">
-        <v>46277</v>
-      </c>
-      <c r="B333" s="44" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C333" s="83">
-        <v>1380</v>
-      </c>
-      <c r="D333" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="E333" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="F333" s="44"/>
-      <c r="G333" s="44"/>
-      <c r="H333" s="44" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I333" s="44" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9">
-      <c r="A334" s="84"/>
-      <c r="B334" s="45"/>
-      <c r="C334" s="85"/>
-      <c r="D334" s="45"/>
-      <c r="E334" s="45"/>
-      <c r="F334" s="46"/>
-      <c r="G334" s="46"/>
-      <c r="H334" s="46"/>
-      <c r="I334" s="45"/>
-    </row>
     <row r="335" spans="1:9">
-      <c r="A335" s="82"/>
-      <c r="B335" s="44"/>
-      <c r="C335" s="83"/>
-      <c r="D335" s="44"/>
-      <c r="E335" s="44"/>
-      <c r="F335" s="44"/>
-      <c r="G335" s="44"/>
-      <c r="H335" s="44"/>
-      <c r="I335" s="44"/>
+      <c r="A335" s="84"/>
+      <c r="B335" s="45"/>
+      <c r="C335" s="85"/>
+      <c r="D335" s="45"/>
+      <c r="E335" s="45"/>
+      <c r="F335" s="46"/>
+      <c r="G335" s="46"/>
+      <c r="H335" s="46"/>
+      <c r="I335" s="45"/>
     </row>
     <row r="336" spans="1:9">
-      <c r="A336" s="84"/>
-      <c r="B336" s="45"/>
-      <c r="C336" s="85"/>
-      <c r="D336" s="45"/>
-      <c r="E336" s="45"/>
-      <c r="F336" s="46"/>
-      <c r="G336" s="46"/>
-      <c r="H336" s="46"/>
-      <c r="I336" s="45"/>
+      <c r="A336" s="82"/>
+      <c r="B336" s="44"/>
+      <c r="C336" s="83"/>
+      <c r="D336" s="44"/>
+      <c r="E336" s="44"/>
+      <c r="F336" s="44"/>
+      <c r="G336" s="44"/>
+      <c r="H336" s="44"/>
+      <c r="I336" s="44"/>
     </row>
     <row r="337" spans="1:9">
-      <c r="A337" s="82"/>
-      <c r="B337" s="44"/>
-      <c r="C337" s="83"/>
-      <c r="D337" s="44"/>
-      <c r="E337" s="44"/>
-      <c r="F337" s="44"/>
-      <c r="G337" s="44"/>
-      <c r="H337" s="44"/>
-      <c r="I337" s="44"/>
+      <c r="A337" s="84"/>
+      <c r="B337" s="45"/>
+      <c r="C337" s="85"/>
+      <c r="D337" s="45"/>
+      <c r="E337" s="45"/>
+      <c r="F337" s="46"/>
+      <c r="G337" s="46"/>
+      <c r="H337" s="46"/>
+      <c r="I337" s="45"/>
     </row>
     <row r="338" spans="1:9">
-      <c r="A338" s="84"/>
-      <c r="B338" s="45"/>
-      <c r="C338" s="85"/>
-      <c r="D338" s="45"/>
-      <c r="E338" s="45"/>
-      <c r="F338" s="46"/>
-      <c r="G338" s="46"/>
-      <c r="H338" s="46"/>
-      <c r="I338" s="45"/>
+      <c r="A338" s="82"/>
+      <c r="B338" s="44"/>
+      <c r="C338" s="83"/>
+      <c r="D338" s="44"/>
+      <c r="E338" s="44"/>
+      <c r="F338" s="44"/>
+      <c r="G338" s="44"/>
+      <c r="H338" s="44"/>
+      <c r="I338" s="44"/>
     </row>
     <row r="339" spans="1:9">
-      <c r="A339" s="82"/>
-      <c r="B339" s="44"/>
-      <c r="C339" s="83"/>
-      <c r="D339" s="44"/>
-      <c r="E339" s="44"/>
-      <c r="F339" s="44"/>
-      <c r="G339" s="44"/>
-      <c r="H339" s="44"/>
-      <c r="I339" s="44"/>
+      <c r="A339" s="84"/>
+      <c r="B339" s="45"/>
+      <c r="C339" s="85"/>
+      <c r="D339" s="45"/>
+      <c r="E339" s="45"/>
+      <c r="F339" s="46"/>
+      <c r="G339" s="46"/>
+      <c r="H339" s="46"/>
+      <c r="I339" s="45"/>
     </row>
     <row r="340" spans="1:9">
-      <c r="A340" s="84"/>
-      <c r="B340" s="45"/>
-      <c r="C340" s="85"/>
-      <c r="D340" s="45"/>
-      <c r="E340" s="45"/>
-      <c r="F340" s="46"/>
-      <c r="G340" s="46"/>
-      <c r="H340" s="46"/>
-      <c r="I340" s="45"/>
+      <c r="A340" s="82"/>
+      <c r="B340" s="44"/>
+      <c r="C340" s="83"/>
+      <c r="D340" s="44"/>
+      <c r="E340" s="44"/>
+      <c r="F340" s="44"/>
+      <c r="G340" s="44"/>
+      <c r="H340" s="44"/>
+      <c r="I340" s="44"/>
     </row>
     <row r="341" spans="1:9">
-      <c r="A341" s="82"/>
-      <c r="B341" s="44"/>
-      <c r="C341" s="83"/>
-      <c r="D341" s="44"/>
-      <c r="E341" s="44"/>
-      <c r="F341" s="44"/>
-      <c r="G341" s="44"/>
-      <c r="H341" s="44"/>
-      <c r="I341" s="44"/>
+      <c r="A341" s="84"/>
+      <c r="B341" s="45"/>
+      <c r="C341" s="85"/>
+      <c r="D341" s="45"/>
+      <c r="E341" s="45"/>
+      <c r="F341" s="46"/>
+      <c r="G341" s="46"/>
+      <c r="H341" s="46"/>
+      <c r="I341" s="45"/>
     </row>
     <row r="342" spans="1:9">
-      <c r="A342" s="84"/>
-      <c r="B342" s="45"/>
-      <c r="C342" s="85"/>
-      <c r="D342" s="45"/>
-      <c r="E342" s="45"/>
-      <c r="F342" s="46"/>
-      <c r="G342" s="46"/>
-      <c r="H342" s="46"/>
-      <c r="I342" s="45"/>
+      <c r="A342" s="82"/>
+      <c r="B342" s="44"/>
+      <c r="C342" s="83"/>
+      <c r="D342" s="44"/>
+      <c r="E342" s="44"/>
+      <c r="F342" s="44"/>
+      <c r="G342" s="44"/>
+      <c r="H342" s="44"/>
+      <c r="I342" s="44"/>
     </row>
     <row r="343" spans="1:9">
-      <c r="A343" s="82"/>
-      <c r="B343" s="44"/>
-      <c r="C343" s="83"/>
-      <c r="D343" s="44"/>
-      <c r="E343" s="44"/>
-      <c r="F343" s="44"/>
-      <c r="G343" s="44"/>
-      <c r="H343" s="44"/>
-      <c r="I343" s="44"/>
+      <c r="A343" s="84"/>
+      <c r="B343" s="45"/>
+      <c r="C343" s="85"/>
+      <c r="D343" s="45"/>
+      <c r="E343" s="45"/>
+      <c r="F343" s="46"/>
+      <c r="G343" s="46"/>
+      <c r="H343" s="46"/>
+      <c r="I343" s="45"/>
     </row>
     <row r="344" spans="1:9">
-      <c r="A344" s="84"/>
-      <c r="B344" s="45"/>
-      <c r="C344" s="85"/>
-      <c r="D344" s="45"/>
-      <c r="E344" s="45"/>
-      <c r="F344" s="46"/>
-      <c r="G344" s="46"/>
-      <c r="H344" s="46"/>
-      <c r="I344" s="45"/>
+      <c r="A344" s="82"/>
+      <c r="B344" s="44"/>
+      <c r="C344" s="83"/>
+      <c r="D344" s="44"/>
+      <c r="E344" s="44"/>
+      <c r="F344" s="44"/>
+      <c r="G344" s="44"/>
+      <c r="H344" s="44"/>
+      <c r="I344" s="44"/>
     </row>
     <row r="345" spans="1:9">
-      <c r="A345" s="82"/>
-      <c r="B345" s="44"/>
-      <c r="C345" s="83"/>
-      <c r="D345" s="44"/>
-      <c r="E345" s="44"/>
-      <c r="F345" s="44"/>
-      <c r="G345" s="44"/>
-      <c r="H345" s="44"/>
-      <c r="I345" s="44"/>
+      <c r="A345" s="84"/>
+      <c r="B345" s="45"/>
+      <c r="C345" s="85"/>
+      <c r="D345" s="45"/>
+      <c r="E345" s="45"/>
+      <c r="F345" s="46"/>
+      <c r="G345" s="46"/>
+      <c r="H345" s="46"/>
+      <c r="I345" s="45"/>
     </row>
     <row r="346" spans="1:9">
-      <c r="A346" s="84"/>
-      <c r="B346" s="45"/>
-      <c r="C346" s="85"/>
-      <c r="D346" s="45"/>
-      <c r="E346" s="45"/>
-      <c r="F346" s="46"/>
-      <c r="G346" s="46"/>
-      <c r="H346" s="46"/>
-      <c r="I346" s="45"/>
+      <c r="A346" s="82"/>
+      <c r="B346" s="44"/>
+      <c r="C346" s="83"/>
+      <c r="D346" s="44"/>
+      <c r="E346" s="44"/>
+      <c r="F346" s="44"/>
+      <c r="G346" s="44"/>
+      <c r="H346" s="44"/>
+      <c r="I346" s="44"/>
     </row>
     <row r="347" spans="1:9">
-      <c r="A347" s="82"/>
-      <c r="B347" s="44"/>
-      <c r="C347" s="83"/>
-      <c r="D347" s="44"/>
-      <c r="E347" s="44"/>
-      <c r="F347" s="44"/>
-      <c r="G347" s="44"/>
-      <c r="H347" s="44"/>
-      <c r="I347" s="44"/>
+      <c r="A347" s="84"/>
+      <c r="B347" s="45"/>
+      <c r="C347" s="85"/>
+      <c r="D347" s="45"/>
+      <c r="E347" s="45"/>
+      <c r="F347" s="46"/>
+      <c r="G347" s="46"/>
+      <c r="H347" s="46"/>
+      <c r="I347" s="45"/>
     </row>
     <row r="348" spans="1:9">
-      <c r="A348" s="84"/>
-      <c r="B348" s="45"/>
-      <c r="C348" s="85"/>
-      <c r="D348" s="45"/>
-      <c r="E348" s="45"/>
-      <c r="F348" s="46"/>
-      <c r="G348" s="46"/>
-      <c r="H348" s="46"/>
-      <c r="I348" s="45"/>
+      <c r="A348" s="82"/>
+      <c r="B348" s="44"/>
+      <c r="C348" s="83"/>
+      <c r="D348" s="44"/>
+      <c r="E348" s="44"/>
+      <c r="F348" s="44"/>
+      <c r="G348" s="44"/>
+      <c r="H348" s="44"/>
+      <c r="I348" s="44"/>
     </row>
     <row r="349" spans="1:9">
-      <c r="A349" s="82"/>
-      <c r="B349" s="44"/>
-      <c r="C349" s="83"/>
-      <c r="D349" s="44"/>
-      <c r="E349" s="44"/>
-      <c r="F349" s="44"/>
-      <c r="G349" s="44"/>
-      <c r="H349" s="44"/>
-      <c r="I349" s="44"/>
+      <c r="A349" s="84"/>
+      <c r="B349" s="45"/>
+      <c r="C349" s="85"/>
+      <c r="D349" s="45"/>
+      <c r="E349" s="45"/>
+      <c r="F349" s="46"/>
+      <c r="G349" s="46"/>
+      <c r="H349" s="46"/>
+      <c r="I349" s="45"/>
     </row>
     <row r="350" spans="1:9">
-      <c r="A350" s="84"/>
-      <c r="B350" s="45"/>
-      <c r="C350" s="85"/>
-      <c r="D350" s="45"/>
-      <c r="E350" s="45"/>
-      <c r="F350" s="46"/>
-      <c r="G350" s="46"/>
-      <c r="H350" s="46"/>
-      <c r="I350" s="45"/>
+      <c r="A350" s="82"/>
+      <c r="B350" s="44"/>
+      <c r="C350" s="83"/>
+      <c r="D350" s="44"/>
+      <c r="E350" s="44"/>
+      <c r="F350" s="44"/>
+      <c r="G350" s="44"/>
+      <c r="H350" s="44"/>
+      <c r="I350" s="44"/>
     </row>
     <row r="351" spans="1:9">
-      <c r="A351" s="82"/>
-      <c r="B351" s="44"/>
-      <c r="C351" s="83"/>
-      <c r="D351" s="44"/>
-      <c r="E351" s="44"/>
-      <c r="F351" s="44"/>
-      <c r="G351" s="44"/>
-      <c r="H351" s="44"/>
-      <c r="I351" s="44"/>
+      <c r="A351" s="84"/>
+      <c r="B351" s="45"/>
+      <c r="C351" s="85"/>
+      <c r="D351" s="45"/>
+      <c r="E351" s="45"/>
+      <c r="F351" s="46"/>
+      <c r="G351" s="46"/>
+      <c r="H351" s="46"/>
+      <c r="I351" s="45"/>
     </row>
     <row r="352" spans="1:9">
-      <c r="A352" s="84"/>
-      <c r="B352" s="45"/>
-      <c r="C352" s="85"/>
-      <c r="D352" s="45"/>
-      <c r="E352" s="45"/>
-      <c r="F352" s="46"/>
-      <c r="G352" s="46"/>
-      <c r="H352" s="46"/>
-      <c r="I352" s="45"/>
+      <c r="A352" s="82"/>
+      <c r="B352" s="44"/>
+      <c r="C352" s="83"/>
+      <c r="D352" s="44"/>
+      <c r="E352" s="44"/>
+      <c r="F352" s="44"/>
+      <c r="G352" s="44"/>
+      <c r="H352" s="44"/>
+      <c r="I352" s="44"/>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353" s="84"/>
+      <c r="B353" s="45"/>
+      <c r="C353" s="85"/>
+      <c r="D353" s="45"/>
+      <c r="E353" s="45"/>
+      <c r="F353" s="46"/>
+      <c r="G353" s="46"/>
+      <c r="H353" s="46"/>
+      <c r="I353" s="45"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I333" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I334" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1256" xr:uid="{00000000-0002-0000-0400-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1257" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Ordered,Pending,Completed,Cancelled"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -28823,7 +28854,7 @@
         <v>0</v>
       </c>
       <c r="L78" s="52" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="M78" s="52"/>
       <c r="N78" s="52" t="s">
@@ -29143,14 +29174,14 @@
         <v>450</v>
       </c>
       <c r="L84" s="52" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="M84" s="52"/>
       <c r="N84" s="52" t="s">
         <v>588</v>
       </c>
       <c r="O84" s="52" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="P84" s="52"/>
       <c r="Q84" s="52"/>
@@ -29249,14 +29280,14 @@
         <v>1045</v>
       </c>
       <c r="L86" s="52" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="M86" s="52"/>
       <c r="N86" s="52" t="s">
         <v>588</v>
       </c>
       <c r="O86" s="52" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="P86" s="52"/>
       <c r="Q86" s="52"/>
@@ -35622,7 +35653,7 @@
         <v>588</v>
       </c>
       <c r="P194" s="47" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="S194" s="47"/>
       <c r="T194" s="47"/>
@@ -35815,14 +35846,14 @@
         <v>934</v>
       </c>
       <c r="L198" s="55" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="M198" s="55"/>
       <c r="N198" s="47" t="s">
         <v>588</v>
       </c>
       <c r="P198" s="47" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="S198" s="47"/>
       <c r="T198" s="47"/>
@@ -35934,7 +35965,7 @@
         <v>995</v>
       </c>
       <c r="B201" s="55" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C201" s="55" t="s">
         <v>95</v>
@@ -35975,7 +36006,7 @@
         <v>588</v>
       </c>
       <c r="P201" s="47" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="S201" s="47"/>
       <c r="T201" s="47"/>
@@ -36121,7 +36152,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="55" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="M204" s="55"/>
       <c r="N204" s="47" t="s">
@@ -36521,7 +36552,7 @@
         <v>2775</v>
       </c>
       <c r="L212" s="55" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="M212" s="55"/>
       <c r="N212" s="47" t="s">
@@ -36825,7 +36856,7 @@
         <v>761</v>
       </c>
       <c r="L218" s="55" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="M218" s="55"/>
       <c r="N218" s="47" t="s">
@@ -37836,7 +37867,7 @@
         <v>676</v>
       </c>
       <c r="P238" s="86" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="S238" s="47"/>
       <c r="T238" s="47"/>
@@ -38839,7 +38870,7 @@
         <v>1301</v>
       </c>
       <c r="B250" s="52" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="C250" s="52" t="s">
         <v>96</v>
@@ -38881,7 +38912,7 @@
         <v>1304</v>
       </c>
       <c r="P250" s="86" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="S250" s="47"/>
       <c r="T250" s="47"/>
@@ -38891,7 +38922,7 @@
         <v>1305</v>
       </c>
       <c r="B251" s="55" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="C251" s="55" t="s">
         <v>96</v>
@@ -38933,7 +38964,7 @@
         <v>1306</v>
       </c>
       <c r="P251" s="86" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="S251" s="47"/>
       <c r="T251" s="47"/>
@@ -38943,7 +38974,7 @@
         <v>1307</v>
       </c>
       <c r="B252" s="52" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="C252" s="52" t="s">
         <v>96</v>
@@ -38985,7 +39016,7 @@
         <v>1306</v>
       </c>
       <c r="P252" s="86" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="S252" s="47"/>
       <c r="T252" s="47"/>
@@ -38995,7 +39026,7 @@
         <v>1308</v>
       </c>
       <c r="B253" s="55" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="C253" s="55" t="s">
         <v>96</v>
@@ -39037,7 +39068,7 @@
         <v>1304</v>
       </c>
       <c r="P253" s="86" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="S253" s="47"/>
       <c r="T253" s="47"/>
@@ -39130,7 +39161,7 @@
         <v>0</v>
       </c>
       <c r="L255" s="55" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="M255" s="55"/>
       <c r="N255" s="47" t="s">
@@ -39374,7 +39405,7 @@
         <v>676</v>
       </c>
       <c r="P260" s="86" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="S260" s="47"/>
       <c r="T260" s="47"/>
@@ -39472,7 +39503,7 @@
         <v>676</v>
       </c>
       <c r="P262" s="86" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="S262" s="47"/>
       <c r="T262" s="47"/>
@@ -46192,7 +46223,7 @@
       </c>
       <c r="B4" s="9">
         <f>IFERROR(SUMIFS(Sales!$C:$C,Sales!$E:$E,$A4,Sales!$I:$I,"Completed"),0)</f>
-        <v>498078</v>
+        <v>500788</v>
       </c>
       <c r="C4" s="9">
         <f>VLOOKUP($A4,PartnerShares!$A$3:$B$5,2,FALSE())</f>
@@ -46200,11 +46231,11 @@
       </c>
       <c r="D4" s="9">
         <f>Summary!$B$4*C4</f>
-        <v>190315.05539999998</v>
+        <v>191218.56939999998</v>
       </c>
       <c r="E4" s="9">
         <f>B4-D4</f>
-        <v>307762.94460000005</v>
+        <v>309569.43060000002</v>
       </c>
       <c r="F4" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A4,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -46212,7 +46243,7 @@
       </c>
       <c r="G4" s="73">
         <f>E4+F4</f>
-        <v>170452.91860000003</v>
+        <v>172259.40460000001</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1">
@@ -46229,11 +46260,11 @@
       </c>
       <c r="D5" s="11">
         <f>Summary!$B$4*C5</f>
-        <v>190200.88920000001</v>
+        <v>191103.86119999998</v>
       </c>
       <c r="E5" s="11">
         <f>B5-D5</f>
-        <v>-130977.88920000001</v>
+        <v>-131880.86119999998</v>
       </c>
       <c r="F5" s="11">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A5,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -46241,7 +46272,7 @@
       </c>
       <c r="G5" s="74">
         <f>E5+F5</f>
-        <v>-59390.847200000004</v>
+        <v>-60293.819199999984</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1">
@@ -46258,11 +46289,11 @@
       </c>
       <c r="D6" s="9">
         <f>Summary!$B$4*C6</f>
-        <v>190315.05539999998</v>
+        <v>191218.56939999998</v>
       </c>
       <c r="E6" s="9">
         <f>B6-D6</f>
-        <v>-177785.05539999998</v>
+        <v>-178688.56939999998</v>
       </c>
       <c r="F6" s="9">
         <f>IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$D$13:$D$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)-IFERROR(SUMIFS(PartnerShares!$E$13:$E$499,PartnerShares!$C$13:$C$499,$A6,PartnerShares!$B$13:$B$499,"Cash"),0)</f>
@@ -46270,7 +46301,7 @@
       </c>
       <c r="G6" s="73">
         <f>E6+F6</f>
-        <v>-112062.07139999997</v>
+        <v>-112965.58539999997</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1">
